--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13 06:15:57</t>
+          <t xml:space="preserve">2026-09-19 13:31:19</t>
         </is>
       </c>
     </row>
@@ -871,433 +871,433 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="32" ht="247.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JMeter 性能試験の実行と実行状況の確認 (compose へ追加された jmeter コンテナを docker compose --profile loadtest run --rm jmeter run &lt;テスト計画&gt; として呼び出し、テスト計画 (.jmx) に設定されているスレッド数・Ramp-Up 期間・ループ回数を上書きして実行する。結果 (result.jtl) と HTML ダッシュボードはレポートファイルと同じディレクトリへ出力する)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(--keep-container-mode logs の「JMeter 性能試験を実行」「JMeter 実行状況を確認」。サービス名・profiles は --jmeter-service / --jmeter-profile、負荷条件は --jmeter-threads / --jmeter-rampup / --jmeter-loops、出力先は --jmeter-report-dir、別端末からの確認は --jmeter-status)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《できること》</t>
         </is>
       </c>
-      <c r="B32" s="8"/>
-    </row>
-    <row r="33" ht="33.0" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup も --verify-url も指定しなければ、純粋にビルドのみを行って終了します
 (従来の build_and_push.sh --build-only 相当)。</t>
         </is>
       </c>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《行わないこと》</t>
         </is>
       </c>
-      <c r="B34" s="8"/>
-    </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
         </is>
       </c>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B36" s="8"/>
-    </row>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="B37" s="8"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">前提</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker、docker compose または docker-compose</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="33.0" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">追加で必要</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS 認証</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param を使う場合のみ必要 (aws login --remote 済み)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B41" s="8"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="B42" s="8"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" ht="9.0" customHeight="1">
-      <c r="A43" s="0"/>
-    </row>
-    <row r="44" ht="24.0" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" ht="9.0" customHeight="1">
+      <c r="A44" s="0"/>
+    </row>
+    <row r="45" ht="24.0" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2. 全体構成</t>
         </is>
       </c>
-      <c r="B44" s="5"/>
-    </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="B45" s="5"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.1 ファイル内のセクション構成》</t>
         </is>
       </c>
-      <c r="B45" s="8"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="B46" s="8"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">位置</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">セクション</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="33.0" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冒頭</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ヘッダーコメント</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目的・機能一覧・使い方</t>
         </is>
       </c>
     </row>
     <row r="48" ht="33.0" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">冒頭</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘッダーコメント</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目的・機能一覧・使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="33.0" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示タイムゾーン設定</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示・保存する時刻をすべて JST に固定</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="82.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="50" ht="82.5" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="49.5" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="51" ht="49.5" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ用ヘルパ</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / run / JST 変換ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">usage()</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--help の本文</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="66.0" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="53" ht="66.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services によるカンマ区切り分割、need_value による値欠落検出</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="49.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54" ht="49.5" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">入力値の検証</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="66.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="56" ht="66.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build コンテキスト / Dockerfile の上書き</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_build_scan / compose_build_rewrite / apply_compose_build_overrides</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="49.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="57" ht="49.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="82.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="82.5" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードの伝搬検証</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="49.5" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="59" ht="49.5" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動確認・ログ表示ヘルパ</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ取得、ANSI 除去、色分け、companion ログ</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="33.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内情報の収集と整形</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="82.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="61" ht="82.5" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ・OpenTelemetry 設定</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/proc/&lt;pid&gt;/cmdline の走査、JVM オプションの分類、OpenTelemetry 設定の突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="66.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="62" ht="66.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対話操作</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="33.0" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 完全クリーンアップ</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="66.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
         </is>
       </c>
     </row>
@@ -1309,29 +1309,29 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="66.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="132.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / Dockerfile (ビルド時) / 起動スクリプト・実行状況 (実行時) の収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1343,29 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / Dockerfile (ビルド時) / 起動スクリプト・実行状況 (実行時) の収集・実行・表示・レポート追記</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="132.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ECS サーキットブレーカ再現</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コンテナの healthcheck 判定、ECS と同じ停止手順 (SIGTERM → stopTimeout → SIGKILL)、jboss-cli の :reload の注入、server.log の切断判定と保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポート</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
@@ -1377,457 +1377,474 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポート</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="49.5" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
+    <row r="70" ht="49.5" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B70" s="8"/>
-    </row>
-    <row r="71" ht="19.5" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="B71" s="8"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="33.0" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
+    <row r="73" ht="33.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・時刻</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力整形と UTC→JST 変換</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="66.0" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
+    <row r="74" ht="66.0" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">引数処理</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services / need_value / validate_positive_integer / validate_non_negative_integer</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証 (ビルド監視の各値は 0 を許す)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="49.5" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="75" ht="49.5" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="82.5" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76" ht="82.5" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build 設定の上書き</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">apply_compose_build_overrides / compose_build_scan / compose_build_rewrite / cleanup_generated_compose_file / compose_file_display</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--base-context などの指定を反映した実効 compose ファイルの生成・検証・後始末 (→ 5.1-2)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="66.0" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="77" ht="66.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">サービスの保護</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">validate_keep_services / resolve_keep_service_targets / service_is_kept / run_compose_build / remove_project_volumes_except_kept / remove_all_images_except_kept / remove_all_volumes_except_kept</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-service の no-cache 除外と、イメージ・ボリュームの保護 (→ 5.1-3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="33.0" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログ表示</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
         </is>
       </c>
     </row>
     <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">URL 確認</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify_url / show_url_body</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">情報表示</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="66.0" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="82" ht="66.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="33.0" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話操作</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">対話操作</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">healthcheck</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
         </is>
       </c>
     </row>
     <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="82.5" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" ht="82.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド監視</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run_build_with_watchdog / build_watchdog_reader / build_watchdog_monitor / diagnose_build_stall / build_phase_from_line / check_build_disk_space</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exporting layers などで出力が途切れたときの進捗表示・停滞診断・上限時間での中断</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="66.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent 送信検証</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
         </is>
       </c>
     </row>
     <row r="88" ht="66.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">cwagent 送信検証</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="66.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">cwagent ロググループ準備</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="165.0" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="90" ht="165.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_war_deploy_exceptions / deploy_exception_output_requested / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / show_war_deploy_exception_outputs / append_deploy_exception_report</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、出力先の要否判定、画面表示 (--deploy-exception-display 指定時)、全量レポートへの記載 (--deploy-exception-report 指定時)、Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="264.0" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="91" ht="264.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用 FS 分析</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / show_readonly_analysis_outputs / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示 (--readonly-analysis-display 指定時)、全量レポートへの記載 (--readonly-analysis-report 指定時)、Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="181.5" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="92" ht="181.5" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS サーキットブレーカ再現</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ecs_cb_check_during_startup / ecs_cb_find_unhealthy_essential / run_ecs_circuit_breaker / ecs_cb_run_stop_cycle / ecs_cb_stop_task / ecs_cb_start_reload / ecs_cb_judge_truncation / ecs_cb_report_logging_config / ecs_cb_replace_task / run_ecs_circuit_breaker_drill / append_ecs_circuit_breaker_report</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動確認中の unhealthy 判定、ECS と同じ停止手順、:reload の重ね合わせ、停止前後の server.log の突き合わせ、logging subsystem の設定の読み取り、タスクの置き換え、画面・テキスト・全量レポートへの出力 (→ 5.15)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="33.0" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
+    <row r="93" ht="33.0" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">レポート</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの生成</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="66.0" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
+    <row r="94" ht="66.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B94" s="8"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="B95" s="8"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
         </is>
       </c>
-      <c r="B95" s="3"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B96" s="8"/>
-    </row>
-    <row r="97" ht="409.0" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="B97" s="8"/>
+    </row>
+    <row r="98" ht="409.0" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
@@ -1862,59 +1879,51 @@
                                    ディスク空き容量を一覧表示して終える</t>
         </is>
       </c>
-      <c r="B97" s="6"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="B98" s="6"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B98" s="8"/>
-    </row>
-    <row r="99" ht="33.0" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="B99" s="8"/>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B99" s="3"/>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B100" s="8"/>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="B101" s="8"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B101" s="3"/>
-    </row>
-    <row r="102" ht="9.0" customHeight="1">
-      <c r="A102" s="0"/>
-    </row>
-    <row r="103" ht="24.0" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" ht="9.0" customHeight="1">
+      <c r="A103" s="0"/>
+    </row>
+    <row r="104" ht="24.0" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B103" s="5"/>
-    </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.1 全体フロー》</t>
-        </is>
-      </c>
-      <c r="B104" s="8"/>
+      <c r="B104" s="5"/>
     </row>
     <row r="105" ht="19.5" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
@@ -1924,8 +1933,16 @@
       </c>
       <c r="B105" s="8"/>
     </row>
-    <row r="106" ht="99.0" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.1 全体フロー》</t>
+        </is>
+      </c>
+      <c r="B106" s="8"/>
+    </row>
+    <row r="107" ht="99.0" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1935,18 +1952,18 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B106" s="3"/>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B107" s="8"/>
-    </row>
-    <row r="108" ht="66.0" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="B108" s="8"/>
+    </row>
+    <row r="109" ht="66.0" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析も同じタイミングで実行します。
 こちらは compose.yml と Dockerfile の定義だけでも判定できるため、
@@ -1954,203 +1971,191 @@
 実行状況からの根拠が無いことを結果へ明記します (6.8 参照)。</t>
         </is>
       </c>
-      <c r="B108" s="3"/>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B109" s="8"/>
-    </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="B110" s="8"/>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
         </is>
       </c>
-      <c r="B110" s="3"/>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B111" s="8"/>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="B112" s="8"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">指定</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未指定</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
         </is>
       </c>
     </row>
     <row r="114" ht="19.5" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">未指定</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">1 個</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そのサービスのみビルド</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="33.0" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2 個以上</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B116" s="8"/>
-    </row>
-    <row r="117" ht="33.0" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="B117" s="8"/>
+    </row>
+    <row r="118" ht="33.0" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B117" s="3"/>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B118" s="8"/>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="B119" s="8"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v2 (docker compose)</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
     <row r="121" ht="19.5" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">v2 (docker compose)</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B122" s="8"/>
-    </row>
-    <row r="123" ht="33.0" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="B123" s="8"/>
+    </row>
+    <row r="124" ht="33.0" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B123" s="3"/>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B124" s="8"/>
-    </row>
-    <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="B125" s="8"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B125" s="3"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B126" s="8"/>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="B127" s="8"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">タイミング</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2167,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
         </is>
       </c>
     </row>
@@ -2174,64 +2179,68 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="19.5" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+    <row r="133" ht="19.5" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B132" s="8"/>
-    </row>
-    <row r="133" ht="33.0" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="B133" s="8"/>
+    </row>
+    <row r="134" ht="33.0" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド自体は監視プロセス付きで実行し、exporting to image / exporting layers で
 出力が途切れても状況が分かるようにします (5.2-2 参照)。</t>
         </is>
       </c>
-      <c r="B133" s="3"/>
-    </row>
-    <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B134" s="8"/>
-    </row>
-    <row r="135" ht="49.5" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="B135" s="8"/>
+    </row>
+    <row r="136" ht="49.5" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド出力は常に控えておき、サービス単位へ切り分けたビルドログを全量レポートとは
 別のファイルへ書き出します。ビルドエラーで終了する実行では、各サービスの
 ビルドログを画面へ全量表示してから終了します (5.2-0-2 参照)。</t>
         </is>
       </c>
-      <c r="B135" s="3"/>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B136" s="8"/>
+      <c r="B136" s="3"/>
     </row>
     <row r="137" ht="19.5" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
@@ -2241,8 +2250,16 @@
       </c>
       <c r="B137" s="8"/>
     </row>
-    <row r="138" ht="148.5" customHeight="1">
-      <c r="A138" s="3" t="inlineStr">
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B138" s="8"/>
+    </row>
+    <row r="139" ht="148.5" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -2255,35 +2272,35 @@
   この判定は起動完了ログの確認より後に行うため、起動が先に完了した実行では動きません</t>
         </is>
       </c>
-      <c r="B138" s="3"/>
-    </row>
-    <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B139" s="8"/>
-    </row>
-    <row r="140" ht="33.0" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
+      <c r="B140" s="8"/>
+    </row>
+    <row r="141" ht="33.0" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B140" s="6"/>
-    </row>
-    <row r="141" ht="19.5" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="B141" s="6"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B141" s="8"/>
-    </row>
-    <row r="142" ht="66.0" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="B142" s="8"/>
+    </row>
+    <row r="143" ht="66.0" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -2291,181 +2308,181 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B142" s="3"/>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B143" s="8"/>
-    </row>
-    <row r="144" ht="33.0" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="B144" s="8"/>
+    </row>
+    <row r="145" ht="33.0" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B144" s="3"/>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" ht="19.5" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B145" s="8"/>
-    </row>
-    <row r="146" ht="19.5" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="B146" s="8"/>
+    </row>
+    <row r="147" ht="19.5" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="19.5" customHeight="1">
-      <c r="A147" s="11" t="inlineStr">
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除 (ボリュームは残す)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="49.5" customHeight="1">
-      <c r="A148" s="11" t="inlineStr">
+    <row r="149" ht="49.5" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down --volumes でボリュームごと削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="33.0" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
+    <row r="150" ht="33.0" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">取り込み検証で「古い成果物を抱えたボリューム」を検出</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down --volumes でボリュームごと削除し、次回の実行で作り直させる (→ 5.13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--remove-volumes 指定</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">この実行が行うすべての compose down へ --volumes を付ける</t>
         </is>
       </c>
     </row>
     <row r="151" ht="19.5" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--remove-volumes 指定</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">この実行が行うすべての compose down へ --volumes を付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-volumes 指定</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">上記いずれの場合もボリュームを残す (従来の動作)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="33.0" customHeight="1">
-      <c r="A152" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
     <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="33.0" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container-after-interaction 指定</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="19.5" customHeight="1">
-      <c r="A154" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
     <row r="155" ht="19.5" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="19.5" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="157" ht="19.5" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B156" s="8"/>
-    </row>
-    <row r="157" ht="49.5" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
+      <c r="B157" s="8"/>
+    </row>
+    <row r="158" ht="49.5" customHeight="1">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B157" s="3"/>
-    </row>
-    <row r="158" ht="19.5" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" ht="19.5" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B158" s="8"/>
-    </row>
-    <row r="159" ht="66.0" customHeight="1">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="B159" s="8"/>
+    </row>
+    <row r="160" ht="66.0" customHeight="1">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2473,34 +2490,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B159" s="3"/>
-    </row>
-    <row r="160" ht="19.5" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B160" s="8"/>
-    </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="3" t="inlineStr">
+      <c r="B161" s="8"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B161" s="3"/>
-    </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" ht="19.5" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B162" s="8"/>
-    </row>
-    <row r="163" ht="148.5" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
+      <c r="B163" s="8"/>
+    </row>
+    <row r="164" ht="148.5" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2513,18 +2530,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B163" s="6"/>
-    </row>
-    <row r="164" ht="19.5" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
+      <c r="B164" s="6"/>
+    </row>
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B164" s="8"/>
-    </row>
-    <row r="165" ht="165.0" customHeight="1">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="B165" s="8"/>
+    </row>
+    <row r="166" ht="165.0" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2538,458 +2555,458 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B165" s="3"/>
-    </row>
-    <row r="166" ht="19.5" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" ht="19.5" customHeight="1">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B166" s="8"/>
-    </row>
-    <row r="167" ht="49.5" customHeight="1">
-      <c r="A167" s="3" t="inlineStr">
+      <c r="B167" s="8"/>
+    </row>
+    <row r="168" ht="49.5" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B167" s="3"/>
-    </row>
-    <row r="168" ht="19.5" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B168" s="8"/>
-    </row>
-    <row r="169" ht="19.5" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
+      <c r="B169" s="8"/>
+    </row>
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B169" s="3"/>
-    </row>
-    <row r="170" ht="9.0" customHeight="1">
-      <c r="A170" s="0"/>
-    </row>
-    <row r="171" ht="24.0" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" ht="9.0" customHeight="1">
+      <c r="A171" s="0"/>
+    </row>
+    <row r="172" ht="24.0" customHeight="1">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B171" s="5"/>
-    </row>
-    <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="B172" s="5"/>
+    </row>
+    <row r="173" ht="19.5" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="33.0" customHeight="1">
-      <c r="A173" s="11" t="inlineStr">
+    <row r="174" ht="33.0" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="409.0" customHeight="1">
-      <c r="A174" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行時エラー</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG、コピーしたファイルの取り込み検証 NG (コンテナ内の中身がコピー元と一致しない / --copy-artifact-required 指定時に未検出)</t>
         </is>
       </c>
     </row>
     <row r="175" ht="409.0" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行時エラー</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG、コピーしたファイルの取り込み検証 NG (コンテナ内の中身がコピー元と一致しない / --copy-artifact-required 指定時に未検出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="409.0" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、--readonly-analysis-display と --no-readonly-analysis の同時指定、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
         </is>
       </c>
-    </row>
-    <row r="176" ht="19.5" customHeight="1">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
-        </is>
-      </c>
-      <c r="B176" s="3"/>
     </row>
     <row r="177" ht="19.5" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
+        </is>
+      </c>
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" ht="19.5" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B177" s="3"/>
-    </row>
-    <row r="178" ht="9.0" customHeight="1">
-      <c r="A178" s="0"/>
-    </row>
-    <row r="179" ht="24.0" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" ht="9.0" customHeight="1">
+      <c r="A179" s="0"/>
+    </row>
+    <row r="180" ht="24.0" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B179" s="5"/>
-    </row>
-    <row r="180" ht="19.5" customHeight="1">
-      <c r="A180" s="8" t="inlineStr">
+      <c r="B180" s="5"/>
+    </row>
+    <row r="181" ht="19.5" customHeight="1">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B180" s="8"/>
-    </row>
-    <row r="181" ht="19.5" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="B181" s="8"/>
+    </row>
+    <row r="182" ht="19.5" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="19.5" customHeight="1">
-      <c r="A182" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="183" ht="19.5" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="184" ht="19.5" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
     <row r="185" ht="19.5" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
     <row r="186" ht="19.5" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="187" ht="19.5" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="188" ht="19.5" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="19.5" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">TERM</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">dumb の場合は色分けしない</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="19.5" customHeight="1">
-      <c r="A189" s="8" t="inlineStr">
+    <row r="190" ht="19.5" customHeight="1">
+      <c r="A190" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B189" s="8"/>
-    </row>
-    <row r="190" ht="19.5" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="B190" s="8"/>
+    </row>
+    <row r="191" ht="19.5" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="19.5" customHeight="1">
-      <c r="A191" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="192" ht="19.5" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="193" ht="19.5" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="19.5" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="19.5" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="33.0" customHeight="1">
-      <c r="A195" s="11" t="inlineStr">
+    <row r="196" ht="33.0" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="19.5" customHeight="1">
-      <c r="A196" s="8" t="inlineStr">
+    <row r="197" ht="19.5" customHeight="1">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B196" s="8"/>
-    </row>
-    <row r="197" ht="49.5" customHeight="1">
-      <c r="A197" s="3" t="inlineStr">
+      <c r="B197" s="8"/>
+    </row>
+    <row r="198" ht="49.5" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B197" s="3"/>
-    </row>
-    <row r="198" ht="19.5" customHeight="1">
-      <c r="A198" s="8" t="inlineStr">
+      <c r="B198" s="3"/>
+    </row>
+    <row r="199" ht="19.5" customHeight="1">
+      <c r="A199" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B198" s="8"/>
-    </row>
-    <row r="199" ht="19.5" customHeight="1">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="B199" s="8"/>
+    </row>
+    <row r="200" ht="19.5" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="33.0" customHeight="1">
-      <c r="A200" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM オプションの受け渡し</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
     <row r="201" ht="33.0" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenTelemetry 標準設定</t>
+          <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
+          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
+          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
     <row r="202" ht="33.0" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">OpenTelemetry 標準設定</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="33.0" customHeight="1">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B202" s="3" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C202" s="3" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="19.5" customHeight="1">
-      <c r="A203" s="11" t="inlineStr">
+    <row r="204" ht="19.5" customHeight="1">
+      <c r="A204" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C203" s="3" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="19.5" customHeight="1">
-      <c r="A204" s="8" t="inlineStr">
+    <row r="205" ht="19.5" customHeight="1">
+      <c r="A205" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B204" s="8"/>
-    </row>
-    <row r="205" ht="19.5" customHeight="1">
-      <c r="A205" s="3" t="inlineStr">
+      <c r="B205" s="8"/>
+    </row>
+    <row r="206" ht="19.5" customHeight="1">
+      <c r="A206" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B205" s="3"/>
+      <c r="B206" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="79">
@@ -2998,17 +3015,16 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A97:B97"/>
@@ -3016,7 +3032,7 @@
     <mergeCell ref="A99:B99"/>
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A102:B102"/>
     <mergeCell ref="A104:B104"/>
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="A106:B106"/>
@@ -3025,15 +3041,15 @@
     <mergeCell ref="A109:B109"/>
     <mergeCell ref="A110:B110"/>
     <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A112:B112"/>
     <mergeCell ref="A117:B117"/>
     <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A119:B119"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="A125:B125"/>
     <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A127:B127"/>
     <mergeCell ref="A133:B133"/>
     <mergeCell ref="A134:B134"/>
     <mergeCell ref="A135:B135"/>
@@ -3047,7 +3063,7 @@
     <mergeCell ref="A143:B143"/>
     <mergeCell ref="A144:B144"/>
     <mergeCell ref="A145:B145"/>
-    <mergeCell ref="A156:B156"/>
+    <mergeCell ref="A146:B146"/>
     <mergeCell ref="A157:B157"/>
     <mergeCell ref="A158:B158"/>
     <mergeCell ref="A159:B159"/>
@@ -3061,17 +3077,18 @@
     <mergeCell ref="A167:B167"/>
     <mergeCell ref="A168:B168"/>
     <mergeCell ref="A169:B169"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="A172:B172"/>
     <mergeCell ref="A177:B177"/>
-    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="A178:B178"/>
     <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A189:B189"/>
-    <mergeCell ref="A196:B196"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="A190:B190"/>
     <mergeCell ref="A197:B197"/>
     <mergeCell ref="A198:B198"/>
-    <mergeCell ref="A204:B204"/>
+    <mergeCell ref="A199:B199"/>
     <mergeCell ref="A205:B205"/>
+    <mergeCell ref="A206:B206"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6775,76 +6792,68 @@
     <row r="125" ht="33.0" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jmeter-service NAME</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">Compose サービス名</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">jmeter</t>
+        </is>
+      </c>
+      <c r="E125" s="7"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
+          <t xml:space="preserve">JMeter 実行コンテナのサービス名 (→ 5.4-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--jmeter-profile NAME</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">profiles 名</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loadtest</t>
+        </is>
+      </c>
+      <c r="E126" s="7"/>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose へ --profile として渡す値</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="33.0" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--no-jmeter-profile</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -6852,371 +6861,331 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E127" s="7"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose へ --profile を渡さない (profiles を使っていない構成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--jmeter-report-dir DIR</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(--report-dir → 一時ディレクトリ)</t>
+        </is>
+      </c>
+      <c r="E128" s="7"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
+          <t xml:space="preserve">結果 (result.jtl / report/index.html / jmeter.log) の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--jmeter-plan FILE</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.jmx のファイル名</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で選択)</t>
+        </is>
+      </c>
+      <c r="E129" s="7"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="19.5" customHeight="1">
+          <t xml:space="preserve">実行するテスト計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--jmeter-threads N</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で入力)</t>
+        </is>
+      </c>
+      <c r="E130" s="7"/>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="49.5" customHeight="1">
+          <t xml:space="preserve">スレッド数 (同時実行ユーザ数) の上書き値</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--jmeter-rampup SEC</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で入力)</t>
+        </is>
+      </c>
+      <c r="E131" s="7"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
+          <t xml:space="preserve">Ramp-Up 期間 (秒) の上書き値</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="33.0" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--jmeter-loops N</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数または -1</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で入力)</t>
+        </is>
+      </c>
+      <c r="E132" s="7"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない</t>
+          <t xml:space="preserve">ループ回数の上書き値 (-1 = 試験時間まで無限に回す)</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--jmeter-target NAME</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">targets.json のキー</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(コンテナの既定)</t>
+        </is>
+      </c>
+      <c r="E133" s="7"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+          <t xml:space="preserve">負荷をかける相手 (frontend / backend / alb など)</t>
         </is>
       </c>
     </row>
     <row r="134" ht="33.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jmeter-duration SEC</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(コンテナの既定)</t>
+        </is>
+      </c>
+      <c r="E134" s="7"/>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">試験時間 (秒)</t>
         </is>
       </c>
     </row>
     <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-jmeter-build</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E135" s="7"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">実行前の compose build &lt;jmeter サービス&gt; を行わない</t>
         </is>
       </c>
     </row>
     <row r="136" ht="33.0" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jmeter-status</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E136" s="7"/>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行状況を表示して終了する (ビルド・起動・後始末をしない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="33.0" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="115.5" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
+      <c r="E138" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="33.0" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7197,7 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -7236,9 +7205,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
@@ -7248,11 +7217,11 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7260,7 +7229,7 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -7268,115 +7237,115 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="19.5" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="E140" s="7" t="inlineStr">
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="33.0" customHeight="1">
-      <c r="A141" s="11" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="33.0" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="49.5" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="33.0" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B143" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
         </is>
       </c>
     </row>
@@ -7388,17 +7357,17 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
@@ -7408,7 +7377,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -7420,17 +7389,17 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
@@ -7440,7 +7409,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
         </is>
       </c>
     </row>
@@ -7452,17 +7421,17 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -7472,7 +7441,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7484,17 +7453,17 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis-display</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
@@ -7504,11 +7473,11 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="49.5" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="33.0" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7516,59 +7485,59 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="115.5" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="33.0" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B149" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -7580,17 +7549,17 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
@@ -7600,11 +7569,11 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="33.0" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7612,17 +7581,17 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
@@ -7632,11 +7601,11 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="33.0" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7644,7 +7613,7 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -7652,9 +7621,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
@@ -7664,11 +7633,11 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="49.5" customHeight="1">
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7676,27 +7645,27 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -7708,17 +7677,17 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -7728,11 +7697,11 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="19.5" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7740,17 +7709,17 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
@@ -7760,11 +7729,11 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7772,17 +7741,17 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -7792,7 +7761,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7773,7 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-display</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -7824,7 +7793,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7805,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -7846,7 +7815,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
@@ -7856,11 +7825,11 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="33.0" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7868,7 +7837,7 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -7878,7 +7847,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
@@ -7888,11 +7857,11 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="49.5" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7900,7 +7869,7 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--readonly-analysis-report</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -7908,9 +7877,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
@@ -7920,7 +7889,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7932,59 +7901,59 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="33.0" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E161" s="7" t="inlineStr">
+      <c r="E162" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7965,7 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -8016,7 +7985,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -8028,7 +7997,7 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-jboss-module-list-text</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -8048,11 +8017,11 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="49.5" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -8060,12 +8029,12 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -8075,12 +8044,12 @@
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -8092,95 +8061,103 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-truststore-inventory-text</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="19.5" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E166" s="7" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="33.0" customHeight="1">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E167" s="7"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="168" ht="33.0" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E168" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="169" ht="33.0" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--undertow-analysis-display</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -8193,22 +8170,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E169" s="7"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="170" ht="33.0" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -8216,471 +8197,623 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E170" s="7"/>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="33.0" customHeight="1">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="33.0" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cert-check-text FILE</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E171" s="7"/>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="33.0" customHeight="1">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B172" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="19.5" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E172" s="7"/>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="49.5" customHeight="1">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B173" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--suppress-syslog</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="33.0" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="19.5" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E173" s="7"/>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="49.5" customHeight="1">
-      <c r="A174" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="33.0" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="33.0" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E174" s="7"/>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="49.5" customHeight="1">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file / local</t>
-        </is>
-      </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file</t>
-        </is>
-      </c>
-      <c r="E175" s="7"/>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="49.5" customHeight="1">
-      <c r="A176" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-audit</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="33.0" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E176" s="7"/>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="49.5" customHeight="1">
-      <c r="A177" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E177" s="7"/>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="49.5" customHeight="1">
-      <c r="A178" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B178" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages</t>
-        </is>
-      </c>
-      <c r="E178" s="7"/>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="19.5" customHeight="1">
-      <c r="A179" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.9 その他</t>
-        </is>
-      </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
       <c r="E179" s="7"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="180" ht="33.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E180" s="7"/>
-      <c r="F180" s="3"/>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="33.0" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E181" s="7"/>
-      <c r="F181" s="3"/>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="33.0" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E182" s="7"/>
-      <c r="F182" s="3"/>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="33.0" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C183" s="3"/>
-      <c r="D183" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E183" s="7"/>
-      <c r="F183" s="3"/>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="33.0" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E184" s="7"/>
-      <c r="F184" s="3"/>
-    </row>
-    <row r="185" ht="33.0" customHeight="1">
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="49.5" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
+          <t xml:space="preserve">--suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="33.0" customHeight="1">
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="49.5" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3"/>
+          <t xml:space="preserve">--no-suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="33.0" customHeight="1">
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="49.5" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
+        </is>
+      </c>
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="49.5" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
+          <t xml:space="preserve">--syslog-audit</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E188" s="7"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="33.0" customHeight="1">
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="49.5" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E189" s="7"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="33.0" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="49.5" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
-        </is>
-      </c>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E190" s="7"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="33.0" customHeight="1">
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="19.5" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C191" s="3"/>
@@ -8688,109 +8821,89 @@
       <c r="E191" s="7"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="192" ht="33.0" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
-        </is>
-      </c>
+      <c r="F192" s="3"/>
     </row>
     <row r="193" ht="33.0" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="7"/>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F193" s="3"/>
     </row>
     <row r="194" ht="33.0" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F194" s="3"/>
     </row>
     <row r="195" ht="33.0" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="7"/>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
+      <c r="F195" s="3"/>
     </row>
     <row r="196" ht="33.0" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="7"/>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F196" s="3"/>
     </row>
     <row r="197" ht="33.0" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
@@ -8800,7 +8913,7 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C197" s="3"/>
@@ -8808,12 +8921,252 @@
       <c r="E197" s="7"/>
       <c r="F197" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="33.0" customHeight="1">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="33.0" customHeight="1">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B199" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="7"/>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="33.0" customHeight="1">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="33.0" customHeight="1">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="33.0" customHeight="1">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="7"/>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="33.0" customHeight="1">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="7"/>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="33.0" customHeight="1">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="7"/>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="33.0" customHeight="1">
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="7"/>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="33.0" customHeight="1">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="7"/>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="33.0" customHeight="1">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="7"/>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="33.0" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="7"/>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="33.0" customHeight="1">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="7"/>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F197"/>
+  <autoFilter ref="A4:F209"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -10700,323 +11053,323 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="19.5" customHeight="1">
+    <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jmeter-service NAME</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">jmeter</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
+          <t xml:space="preserve">JMeter 実行コンテナのサービス名 (→ 5.4-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--jmeter-profile NAME</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">loadtest</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose へ --profile として渡す値</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--jmeter-report-dir DIR</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
+          <t xml:space="preserve">(--report-dir → 一時ディレクトリ)</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">結果 (result.jtl / report/index.html / jmeter.log) の出力先</t>
         </is>
       </c>
     </row>
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--jmeter-plan FILE</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
+          <t xml:space="preserve">(対話で選択)</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="49.5" customHeight="1">
+          <t xml:space="preserve">実行するテスト計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--jmeter-threads N</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
+          <t xml:space="preserve">(対話で入力)</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
+          <t xml:space="preserve">スレッド数 (同時実行ユーザ数) の上書き値</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--jmeter-rampup SEC</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
+          <t xml:space="preserve">(対話で入力)</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない</t>
+          <t xml:space="preserve">Ramp-Up 期間 (秒) の上書き値</t>
         </is>
       </c>
     </row>
     <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jmeter-loops N</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">(対話で入力)</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ループ回数の上書き値 (-1 = 試験時間まで無限に回す)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--jmeter-target NAME</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">(コンテナの既定)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">負荷をかける相手 (frontend / backend / alb など)</t>
         </is>
       </c>
     </row>
     <row r="104" ht="33.0" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jmeter-duration SEC</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(コンテナの既定)</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">試験時間 (秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="33.0" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="33.0" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="49.5" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="49.5" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="33.0" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -11026,310 +11379,382 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="49.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="49.5" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="49.5" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="49.5" customHeight="1">
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="33.0" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="9.0" customHeight="1">
-      <c r="A116" s="0"/>
-    </row>
-    <row r="117" ht="24.0" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-display</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="49.5" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-report</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="33.0" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="33.0" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">保護の対象</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
-        </is>
-      </c>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="49.5" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に対話シェル (root 実行を禁止する設定では接続できない)</t>
-        </is>
-      </c>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-    </row>
-    <row r="122" ht="33.0" customHeight="1">
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="49.5" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
-        </is>
-      </c>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-    </row>
-    <row r="123" ht="33.0" customHeight="1">
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="49.5" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
-        </is>
-      </c>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-    </row>
-    <row r="124" ht="33.0" customHeight="1">
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="49.5" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
-        </is>
-      </c>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-    </row>
-    <row r="125" ht="33.0" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
-        </is>
-      </c>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
-        </is>
-      </c>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-    </row>
-    <row r="127" ht="33.0" customHeight="1">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
-        </is>
-      </c>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="9.0" customHeight="1">
+      <c r="A125" s="0"/>
+    </row>
+    <row r="126" ht="24.0" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" ht="49.5" customHeight="1">
+    <row r="129" ht="19.5" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
+          <t xml:space="preserve">保護の対象</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
+          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
         </is>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" ht="33.0" customHeight="1">
+    <row r="130" ht="49.5" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
+          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に対話シェル (root 実行を禁止する設定では接続できない)</t>
         </is>
       </c>
       <c r="C130" s="3"/>
@@ -11338,12 +11763,12 @@
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
+          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
         </is>
       </c>
       <c r="C131" s="3"/>
@@ -11352,12 +11777,12 @@
     <row r="132" ht="33.0" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -11366,26 +11791,26 @@
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
         </is>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" ht="49.5" customHeight="1">
+    <row r="134" ht="33.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
         </is>
       </c>
       <c r="C134" s="3"/>
@@ -11394,54 +11819,54 @@
     <row r="135" ht="19.5" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
         </is>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" ht="49.5" customHeight="1">
+    <row r="136" ht="33.0" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" ht="19.5" customHeight="1">
+    <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
         </is>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" ht="33.0" customHeight="1">
+    <row r="138" ht="49.5" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
+          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
         </is>
       </c>
       <c r="C138" s="3"/>
@@ -11450,12 +11875,12 @@
     <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
+          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
         </is>
       </c>
       <c r="C139" s="3"/>
@@ -11464,12 +11889,12 @@
     <row r="140" ht="33.0" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
         </is>
       </c>
       <c r="C140" s="3"/>
@@ -11478,86 +11903,212 @@
     <row r="141" ht="33.0" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
     </row>
-    <row r="142" ht="19.5" customHeight="1">
+    <row r="142" ht="33.0" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" ht="33.0" customHeight="1">
+    <row r="143" ht="49.5" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" ht="33.0" customHeight="1">
+    <row r="144" ht="19.5" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" ht="33.0" customHeight="1">
+    <row r="145" ht="49.5" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" ht="33.0" customHeight="1">
+    <row r="146" ht="19.5" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
         </is>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
+    </row>
+    <row r="147" ht="33.0" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose で何をするのか</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
+        </is>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+    </row>
+    <row r="148" ht="33.0" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
+        </is>
+      </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+    </row>
+    <row r="149" ht="33.0" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 出力ファイル</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+        </is>
+      </c>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+    </row>
+    <row r="150" ht="33.0" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行タイミングと前提</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+        </is>
+      </c>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行タイミングと前提</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+        </is>
+      </c>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+    </row>
+    <row r="152" ht="33.0" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+    </row>
+    <row r="153" ht="33.0" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+    </row>
+    <row r="154" ht="33.0" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+    </row>
+    <row r="155" ht="33.0" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="51">
@@ -11582,16 +12133,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="A126:D126"/>
     <mergeCell ref="B127:D127"/>
     <mergeCell ref="B128:D128"/>
     <mergeCell ref="B129:D129"/>
@@ -11612,6 +12154,15 @@
     <mergeCell ref="B144:D144"/>
     <mergeCell ref="B145:D145"/>
     <mergeCell ref="B146:D146"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="B150:D150"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="B152:D152"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="B154:D154"/>
+    <mergeCell ref="B155:D155"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11878,34 +12429,88 @@
     <row r="17" ht="66.0" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">10-4</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動後に JMeter で性能試験を行う (対話で計画とスレッド数 / Ramp-Up / ループを指定)
+結果 (result.jtl) と HTML レポートは --report-dir と同じディレクトリへ出る</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --keep-container-mode logs --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66.0" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-5</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">負荷条件をあらかじめ決めておき、対話での入力を省く</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --keep-container-mode logs --report-dir ./reports \
+  --jmeter-plan sample-frontend.jmx --jmeter-threads 200 --jmeter-rampup 200 --jmeter-loops -1 \
+  --jmeter-target frontend --jmeter-duration 600</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-6</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">背面で走らせた性能試験の進捗を、別の端末から確認する</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --jmeter-status --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66.0" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートを保存 (ツリーは画面・レポートとも既定では出さない)
 (JVM パラメータと OpenTelemetry 設定は指定不要で同じレポートへ保存される)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --report-dir ./reports</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="49.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="21" ht="49.5" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11-2</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">画面にもレポートにもコンテナ内ツリーを出す
 --directory-tree-depth / --directory-file-limit を付けると画面表示は自動で有効になる</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --report-dir ./reports --directory-tree-report \
@@ -11913,125 +12518,125 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="33.0" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="22" ht="33.0" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11-3</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">画面には出さず、全量レポートにだけツリーを残す</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --report-dir ./reports --directory-tree-report</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="23" ht="33.0" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ構造を環境変数から特定して表示 (指定すると画面表示が有効になる)</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --deployment-dir-env JBOSS_HOME,APP_DEPLOY_DIR</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="49.5" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="24" ht="49.5" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">認証情報を一時配置してビルド
 (コピー先に .npmrc があっても強制上書きし、終了時に元のファイルへ戻す)</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="33.0" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13-2</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー先の既存ファイルには一切触れず、あれば中止する</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file-no-overwrite --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33.0" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26" ht="33.0" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアのマスターパスワードを使ってビルド</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --jboss-password-param /j1/jboss/master-password</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="66.0" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="27" ht="66.0" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-2</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードが実行時の値まで一致しているかを検証
 (standalone.xml と CredentialStore まで見るので起動確認と併用する)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">export JBOSS_MASTER_PASSWORD='pa$w#o"r`d&amp;x'
 ./build_and_verify.sh --verify-startup --verify-jboss-password</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="49.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="28" ht="49.5" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-3</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得した値で検証し、平文は伏せる</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --jboss-password-param /j1/jboss/master-password \
@@ -12039,18 +12644,18 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="49.5" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="29" ht="49.5" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-4</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">既定以外のパスに設定ファイル・CredentialStore がある場合</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --verify-jboss-password \
     --jboss-config-file /opt/eap/standalone/configuration/standalone-full.xml \
@@ -12058,37 +12663,37 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="66.0" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="30" ht="66.0" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-5</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent の設定ファイルチェックとコンテナ内設定の照合を行う
 (compose.yml に cwagent があれば自動。送達レポートは既定では行わない)</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="66.0" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="31" ht="66.0" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-6</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">送達レポートまで行い、送達待ちを 3 分へ延ばして届かなければビルド失敗とする</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app \
@@ -12097,19 +12702,19 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="66.0" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="32" ht="66.0" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-7</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">実 CloudWatch Logs のロググループへ届いたかを aws logs で確認する
 (ロググループが無ければ設定ファイルの名前で作成してから確認する)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent --startup-service app \
@@ -12118,101 +12723,101 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="33.0" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">検証後に Docker を完全クリーンアップ (確認フレーズ入力が必要)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --cleanup-all-docker-data</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="82.5" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="34" ht="82.5" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-2</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
 旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
 実行前からの増減を表示する</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
     --disk-usage-report --prune-build-cache-keep 10GB</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-3</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="33.0" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="36" ht="33.0" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-4</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="33.0" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="115.5" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="38" ht="115.5" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートへ Java 例外解析を残す
 (reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
@@ -12220,7 +12825,7 @@
 画面表示も Excel / テキストの出力も行わない)</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12229,18 +12834,18 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="82.5" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="39" ht="82.5" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12250,19 +12855,19 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="66.0" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="40" ht="66.0" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する
 (テキストは --deploy-exception-text を指定したときだけ出力される)</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12271,30 +12876,30 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-4</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (解析処理ごと省く)</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="181.5" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="42" ht="181.5" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-5</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -12304,7 +12909,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12313,18 +12918,18 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="66.0" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="43" ht="66.0" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-6</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12333,19 +12938,19 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="66.0" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="44" ht="66.0" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-7</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面でも読む
 既定では画面へ出さず、Excel / テキストへ残すだけ</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12353,65 +12958,65 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="33.0" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="45" ht="33.0" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-8</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="66.0" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="46" ht="66.0" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="33.0" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="47" ht="33.0" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="132.0" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="48" ht="132.0" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS サーキットブレーカによるタスク停止の再現 (既定で有効)
 必須コンテナの healthcheck が unhealthy になった実行でだけ動く。
@@ -12419,7 +13024,7 @@
 停止前後の server.log を突き合わせて切れ方まで判定する</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12427,19 +13032,19 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="66.0" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="49" ht="66.0" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-2</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">正常に起動する構成でも、事象を手元で起こしてみる
 (動作確認をすべて終えた後に 1 回だけ停止する。置き換えは行わない)</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12447,53 +13052,53 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="33.0" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="50" ht="33.0" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-3</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">SIGKILL を早めて reload との重なりを作りやすくする</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --ecs-stop-timeout 5 --ecs-circuit-breaker-reload-delay 0</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="33.0" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-4</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">切断の要因を切り分ける (reload を挟まず、停止だけを再現する)</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker-reload</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="33.0" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-5</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">再現を行わない (従来どおり、unhealthy でも止めない)</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker</t>
         </is>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19 13:31:19</t>
+          <t xml:space="preserve">2026-09-24 22:19:59</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="115.5" customHeight="1">
+    <row r="149" ht="148.5" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。logs モードの server.log の FD 点検 / ログ設定の静的点検の結果 (..._server_log_fd_&lt;サービス名&gt;.txt / ..._logging_config_audit_&lt;サービス名&gt;.txt) も同じディレクトリへ出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -11886,29 +11886,29 @@
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" ht="33.0" customHeight="1">
+    <row r="140" ht="82.5" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
+          <t xml:space="preserve">対象の特定 / 起動中の JVM (argv[0] が java で jboss-modules.jar / -Djboss.home.dir を持つもの) の引数から、ログディレクトリを -Djboss.server.log.dir → -Djboss.server.base.dir 配下の log → -Djboss.home.dir 配下の standalone/log → JBOSS_HOME の候補の順に決める。そこで誰も開いていなければ、実際に server.log* が開かれている場所へ切り替える / JBOSS_HOME は JVM の -Djboss.home.dir → 環境変数 → 既定の候補、設定ファイルは --jboss-config-file → JVM の -c → standalone.xml、デプロイ先は deployment-scanner の path / relative-to</t>
         </is>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" ht="33.0" customHeight="1">
+    <row r="141" ht="49.5" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (docker exec -u)。/proc/&lt;pid&gt;/fd は同じユーザーか CAP_SYS_PTRACE でしか読めず、Docker の既定の権限では root でも別ユーザーの FD は見えないため。読めなかったプロセスは [情報] で一覧にする / コンテナの既定ユーザー。権限で読めない cron のディレクトリは [情報] で示す</t>
         </is>
       </c>
       <c r="C141" s="3"/>
@@ -11917,40 +11917,40 @@
     <row r="142" ht="33.0" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
         </is>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" ht="49.5" customHeight="1">
+    <row r="143" ht="33.0" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" ht="19.5" customHeight="1">
+    <row r="144" ht="33.0" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C144" s="3"/>
@@ -11959,12 +11959,12 @@
     <row r="145" ht="49.5" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C145" s="3"/>
@@ -11973,40 +11973,40 @@
     <row r="146" ht="19.5" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" ht="33.0" customHeight="1">
+    <row r="147" ht="49.5" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
+          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
         </is>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" ht="33.0" customHeight="1">
+    <row r="148" ht="19.5" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
+          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
         </is>
       </c>
       <c r="C148" s="3"/>
@@ -12015,12 +12015,12 @@
     <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
         </is>
       </c>
       <c r="C149" s="3"/>
@@ -12029,26 +12029,26 @@
     <row r="150" ht="33.0" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
         </is>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" ht="19.5" customHeight="1">
+    <row r="151" ht="33.0" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C151" s="3"/>
@@ -12057,26 +12057,26 @@
     <row r="152" ht="33.0" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
         </is>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" ht="33.0" customHeight="1">
+    <row r="153" ht="19.5" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
         </is>
       </c>
       <c r="C153" s="3"/>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -12099,19 +12099,47 @@
     <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
+    <row r="156" ht="33.0" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+    </row>
+    <row r="157" ht="33.0" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="53">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -12163,6 +12191,8 @@
     <mergeCell ref="B153:D153"/>
     <mergeCell ref="B154:D154"/>
     <mergeCell ref="B155:D155"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="B157:D157"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24 22:19:59</t>
+          <t xml:space="preserve">2026-09-25 06:41:08</t>
         </is>
       </c>
     </row>
@@ -8469,59 +8469,63 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="33.0" customHeight="1">
+    <row r="179" ht="82.5" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--backend-port-offset N</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E179" s="7"/>
+          <t xml:space="preserve">0〜55545 の整数</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10000</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">ログ設定の静的点検 (--keep-container-mode logs の操作) で jboss-cli.sh --connect の管理ポート 9990 へ加算する backend の port-offset。サービス名に backend を含むサービスは --controller=localhost:&lt;9990 + N&gt; (既定 19990) で接続し、それ以外は 0 (9990)。JVM の -Djboss.socket.binding.port-offset があればそちらを優先</t>
         </is>
       </c>
     </row>
     <row r="180" ht="33.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -8533,23 +8537,23 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8565,7 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -8577,7 +8581,7 @@
       <c r="E182" s="7"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -8589,23 +8593,23 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
@@ -8617,35 +8621,35 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="49.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="33.0" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--disk-usage-report</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -8653,15 +8657,15 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D185" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8677,7 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
+          <t xml:space="preserve">--suppress-syslog</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -8681,15 +8685,15 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
         </is>
       </c>
     </row>
@@ -8701,23 +8705,23 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--no-suppress-syslog</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file / local</t>
-        </is>
-      </c>
-      <c r="D187" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
         </is>
       </c>
     </row>
@@ -8729,23 +8733,23 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit</t>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
         </is>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8761,7 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
+          <t xml:space="preserve">--syslog-audit</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -8765,15 +8769,15 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D189" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
         </is>
       </c>
     </row>
@@ -8785,61 +8789,73 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">--no-syslog-audit</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="19.5" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="49.5" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E191" s="7"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="33.0" customHeight="1">
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="19.5" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="3"/>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="33.0" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
@@ -8849,7 +8865,7 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C193" s="3"/>
@@ -8865,7 +8881,7 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C194" s="3"/>
@@ -8881,7 +8897,7 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C195" s="3"/>
@@ -8897,7 +8913,7 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C196" s="3"/>
@@ -8908,22 +8924,18 @@
     <row r="197" ht="33.0" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="7"/>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F197" s="3"/>
     </row>
     <row r="198" ht="33.0" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
@@ -8933,7 +8945,7 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C198" s="3"/>
@@ -8941,7 +8953,7 @@
       <c r="E198" s="7"/>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8965,7 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C199" s="3"/>
@@ -8961,7 +8973,7 @@
       <c r="E199" s="7"/>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8985,7 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C200" s="3"/>
@@ -8981,7 +8993,7 @@
       <c r="E200" s="7"/>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -8993,7 +9005,7 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C201" s="3"/>
@@ -9001,7 +9013,7 @@
       <c r="E201" s="7"/>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9025,7 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C202" s="3"/>
@@ -9021,7 +9033,7 @@
       <c r="E202" s="7"/>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9045,7 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C203" s="3"/>
@@ -9041,7 +9053,7 @@
       <c r="E203" s="7"/>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9065,7 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C204" s="3"/>
@@ -9061,7 +9073,7 @@
       <c r="E204" s="7"/>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9085,7 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C205" s="3"/>
@@ -9081,7 +9093,7 @@
       <c r="E205" s="7"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9105,7 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C206" s="3"/>
@@ -9101,7 +9113,7 @@
       <c r="E206" s="7"/>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9125,7 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C207" s="3"/>
@@ -9121,7 +9133,7 @@
       <c r="E207" s="7"/>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9145,7 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-file-limit all</t>
         </is>
       </c>
       <c r="C208" s="3"/>
@@ -9141,7 +9153,7 @@
       <c r="E208" s="7"/>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9165,7 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C209" s="3"/>
@@ -9161,12 +9173,32 @@
       <c r="E209" s="7"/>
       <c r="F209" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="33.0" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="7"/>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F209"/>
+  <autoFilter ref="A4:F210"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -11581,47 +11613,47 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="33.0" customHeight="1">
+    <row r="120" ht="82.5" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--backend-port-offset N</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10000</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ログ設定の静的点検 (--keep-container-mode logs の操作) で jboss-cli.sh --connect の管理ポート 9990 へ加算する backend の port-offset。サービス名に backend を含むサービスは --controller=localhost:&lt;9990 + N&gt; (既定 19990) で接続し、それ以外は 0 (9990)。JVM の -Djboss.socket.binding.port-offset があればそちらを優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="33.0" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">有効</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="49.5" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--suppress-syslog</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
         </is>
       </c>
     </row>
@@ -11633,17 +11665,17 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--suppress-syslog</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
         </is>
       </c>
     </row>
@@ -11655,17 +11687,17 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">json-file</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
         </is>
       </c>
     </row>
@@ -11677,90 +11709,98 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="49.5" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--syslog-audit-file FILE</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">/var/log/messages</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="9.0" customHeight="1">
-      <c r="A125" s="0"/>
-    </row>
-    <row r="126" ht="24.0" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="126" ht="9.0" customHeight="1">
+      <c r="A126" s="0"/>
+    </row>
+    <row r="127" ht="24.0" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-    </row>
-    <row r="128" ht="33.0" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129" ht="33.0" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">保護の対象</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
         </is>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" ht="49.5" customHeight="1">
+    <row r="130" ht="19.5" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
+          <t xml:space="preserve">保護の対象</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に対話シェル (root 実行を禁止する設定では接続できない)</t>
+          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
         </is>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" ht="33.0" customHeight="1">
+    <row r="131" ht="49.5" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -11768,7 +11808,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
+          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に対話シェル (root 実行を禁止する設定では接続できない)</t>
         </is>
       </c>
       <c r="C131" s="3"/>
@@ -11782,7 +11822,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
+          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -11796,7 +11836,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
+          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
         </is>
       </c>
       <c r="C133" s="3"/>
@@ -11810,13 +11850,13 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
+          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
         </is>
       </c>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" ht="19.5" customHeight="1">
+    <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -11824,21 +11864,21 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
+          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
         </is>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" ht="33.0" customHeight="1">
+    <row r="136" ht="19.5" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
         </is>
       </c>
       <c r="C136" s="3"/>
@@ -11847,18 +11887,18 @@
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" ht="49.5" customHeight="1">
+    <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
@@ -11866,41 +11906,41 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
         </is>
       </c>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" ht="33.0" customHeight="1">
+    <row r="139" ht="49.5" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
+          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
         </is>
       </c>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" ht="82.5" customHeight="1">
+    <row r="140" ht="33.0" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対象の特定 / 起動中の JVM (argv[0] が java で jboss-modules.jar / -Djboss.home.dir を持つもの) の引数から、ログディレクトリを -Djboss.server.log.dir → -Djboss.server.base.dir 配下の log → -Djboss.home.dir 配下の standalone/log → JBOSS_HOME の候補の順に決める。そこで誰も開いていなければ、実際に server.log* が開かれている場所へ切り替える / JBOSS_HOME は JVM の -Djboss.home.dir → 環境変数 → 既定の候補、設定ファイルは --jboss-config-file → JVM の -c → standalone.xml、デプロイ先は deployment-scanner の path / relative-to</t>
+          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
         </is>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" ht="49.5" customHeight="1">
+    <row r="141" ht="82.5" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
@@ -11908,147 +11948,147 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (docker exec -u)。/proc/&lt;pid&gt;/fd は同じユーザーか CAP_SYS_PTRACE でしか読めず、Docker の既定の権限では root でも別ユーザーの FD は見えないため。読めなかったプロセスは [情報] で一覧にする / コンテナの既定ユーザー。権限で読めない cron のディレクトリは [情報] で示す</t>
+          <t xml:space="preserve">対象の特定 / 起動中の JVM (argv[0] が java で jboss-modules.jar / -Djboss.home.dir を持つもの) の引数から、ログディレクトリを -Djboss.server.log.dir → -Djboss.server.base.dir 配下の log → -Djboss.home.dir 配下の standalone/log → JBOSS_HOME の候補の順に決める。そこで誰も開いていなければ、実際に server.log* が開かれている場所へ切り替える / JBOSS_HOME は JVM の -Djboss.home.dir → 環境変数 → 既定の候補、設定ファイルは --jboss-config-file → JVM の -c → standalone.xml、デプロイ先は deployment-scanner の path / relative-to</t>
         </is>
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
     </row>
-    <row r="142" ht="33.0" customHeight="1">
+    <row r="142" ht="49.5" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
+          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (docker exec -u)。/proc/&lt;pid&gt;/fd は同じユーザーか CAP_SYS_PTRACE でしか読めず、Docker の既定の権限では root でも別ユーザーの FD は見えないため。読めなかったプロセスは [情報] で一覧にする / コンテナの既定ユーザー。権限で読めない cron のディレクトリは [情報] で示す</t>
         </is>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" ht="33.0" customHeight="1">
+    <row r="143" ht="99.0" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">元のスクリプトからの読み替え / ログディレクトリの自動特定、JVM と同じ uid:gid での実行、収集結果を一時ファイルではなく変数に持つ (読み取り専用のルートでも動く) / WAR / EAR を unzip (Info-ZIP / BusyBox) → python3 → jar → bsdtar → busybox unzip の順で読む (元は unzip だけ)、find が無ければシェルの展開で辿る、use-deployment-logging-config を要素の形 (&lt;… value="false"/&gt;) で判定、起動スクリプトを ENTRYPOINT / CMD から自動で点検 (起動コマンドは標準入力で渡す)、実行時設定を常に取得、jboss-cli.sh の接続先は port-offset を考慮 (backend サービスは既定で 9990 + 10000 = 19990。下記)、jboss.server.log.dir 内の別ファイル (app.log 等) を指すだけなら [情報]</t>
         </is>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" ht="33.0" customHeight="1">
+    <row r="144" ht="49.5" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">サービス名に backend を含む (--backend-context と同じ判定) / --backend-port-offset (既定 10000) / --connect --controller=localhost:19990</t>
         </is>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" ht="49.5" customHeight="1">
+    <row r="145" ht="33.0" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" ht="19.5" customHeight="1">
+    <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" ht="49.5" customHeight="1">
+    <row r="147" ht="33.0" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" ht="19.5" customHeight="1">
+    <row r="148" ht="49.5" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" ht="33.0" customHeight="1">
+    <row r="149" ht="19.5" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" ht="33.0" customHeight="1">
+    <row r="150" ht="49.5" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
+          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
+          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
         </is>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" ht="33.0" customHeight="1">
+    <row r="151" ht="19.5" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
         </is>
       </c>
       <c r="C151" s="3"/>
@@ -12057,26 +12097,26 @@
     <row r="152" ht="33.0" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
         </is>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" ht="19.5" customHeight="1">
+    <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
         </is>
       </c>
       <c r="C153" s="3"/>
@@ -12085,12 +12125,12 @@
     <row r="154" ht="33.0" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -12099,26 +12139,26 @@
     <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
         </is>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" ht="33.0" customHeight="1">
+    <row r="156" ht="19.5" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
         </is>
       </c>
       <c r="C156" s="3"/>
@@ -12127,19 +12167,61 @@
     <row r="157" ht="33.0" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
     </row>
+    <row r="158" ht="33.0" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+    </row>
+    <row r="159" ht="33.0" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+    </row>
+    <row r="160" ht="33.0" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="55">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -12161,8 +12243,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="A127:D127"/>
     <mergeCell ref="B128:D128"/>
     <mergeCell ref="B129:D129"/>
     <mergeCell ref="B130:D130"/>
@@ -12193,6 +12274,9 @@
     <mergeCell ref="B155:D155"/>
     <mergeCell ref="B156:D156"/>
     <mergeCell ref="B157:D157"/>
+    <mergeCell ref="B158:D158"/>
+    <mergeCell ref="B159:D159"/>
+    <mergeCell ref="B160:D160"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25 06:41:08</t>
+          <t xml:space="preserve">2026-09-26 19:50:36</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="148.5" customHeight="1">
+    <row r="149" ht="181.5" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。logs モードの server.log の FD 点検 / ログ設定の静的点検の結果 (..._server_log_fd_&lt;サービス名&gt;.txt / ..._logging_config_audit_&lt;サービス名&gt;.txt) も同じディレクトリへ出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。logs モードの server.log の FD 点検 / ログ設定の静的点検の結果 (..._server_log_fd_&lt;サービス名&gt;.txt / ..._logging_config_audit_&lt;サービス名&gt;.txt) も同じディレクトリへ出力。ログローテーションのタイムゾーン点検の結果 (..._log_rotation_tz_&lt;サービス名&gt;.md) も既定で同じディレクトリへ出力 (--no-log-rotation-tz-md で抑制)。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -8501,71 +8501,79 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="33.0" customHeight="1">
+    <row r="180" ht="66.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--log-rotation-tz-md FILE</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E180" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (--keep-container-mode logs の操作) の結果を Markdown で出力する先。未指定時は --report-dir 配下 (無ければ一時ディレクトリ) へ build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md として自動命名。--no-log-rotation-tz-md とは排他</t>
         </is>
       </c>
     </row>
     <row r="181" ht="33.0" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-log-rotation-tz-md</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D181" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E181" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検の Markdown 出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="182" ht="33.0" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -8581,7 +8589,7 @@
       <c r="E182" s="7"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -8593,23 +8601,23 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -8621,23 +8629,23 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8657,7 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -8665,47 +8673,47 @@
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="49.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="33.0" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D186" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="49.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="33.0" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
+          <t xml:space="preserve">--disk-usage-report</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -8721,7 +8729,7 @@
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
         </is>
       </c>
     </row>
@@ -8733,23 +8741,23 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--suppress-syslog</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file / local</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8769,7 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit</t>
+          <t xml:space="preserve">--no-suppress-syslog</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -8777,7 +8785,7 @@
       <c r="E189" s="7"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
         </is>
       </c>
     </row>
@@ -8789,23 +8797,23 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">json-file / local</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">json-file</t>
         </is>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
         </is>
       </c>
     </row>
@@ -8817,77 +8825,101 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">--syslog-audit</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D191" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="19.5" customHeight="1">
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="49.5" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C192" s="3"/>
-      <c r="D192" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E192" s="7"/>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="33.0" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="49.5" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E193" s="7"/>
-      <c r="F193" s="3"/>
-    </row>
-    <row r="194" ht="33.0" customHeight="1">
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="19.5" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="3"/>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="33.0" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
@@ -8897,7 +8929,7 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C195" s="3"/>
@@ -8913,7 +8945,7 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C196" s="3"/>
@@ -8929,7 +8961,7 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C197" s="3"/>
@@ -8940,42 +8972,34 @@
     <row r="198" ht="33.0" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="7"/>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F198" s="3"/>
     </row>
     <row r="199" ht="33.0" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="7"/>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F199" s="3"/>
     </row>
     <row r="200" ht="33.0" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
@@ -8985,7 +9009,7 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C200" s="3"/>
@@ -8993,7 +9017,7 @@
       <c r="E200" s="7"/>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9029,7 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C201" s="3"/>
@@ -9013,7 +9037,7 @@
       <c r="E201" s="7"/>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9049,7 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C202" s="3"/>
@@ -9033,7 +9057,7 @@
       <c r="E202" s="7"/>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9069,7 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C203" s="3"/>
@@ -9053,7 +9077,7 @@
       <c r="E203" s="7"/>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9089,7 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C204" s="3"/>
@@ -9073,7 +9097,7 @@
       <c r="E204" s="7"/>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9109,7 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C205" s="3"/>
@@ -9093,7 +9117,7 @@
       <c r="E205" s="7"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9129,7 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C206" s="3"/>
@@ -9113,7 +9137,7 @@
       <c r="E206" s="7"/>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9149,7 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C207" s="3"/>
@@ -9133,7 +9157,7 @@
       <c r="E207" s="7"/>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9169,7 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C208" s="3"/>
@@ -9153,7 +9177,7 @@
       <c r="E208" s="7"/>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9189,7 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C209" s="3"/>
@@ -9173,7 +9197,7 @@
       <c r="E209" s="7"/>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9209,7 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--directory-file-limit all</t>
         </is>
       </c>
       <c r="C210" s="3"/>
@@ -9193,12 +9217,52 @@
       <c r="E210" s="7"/>
       <c r="F210" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="33.0" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="7"/>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="33.0" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="7"/>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F210"/>
+  <autoFilter ref="A4:F212"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -11999,12 +12063,12 @@
     <row r="145" ht="33.0" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
+          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (/proc/&lt;pid&gt;/environ を読むため)。検出できなければコンテナの既定ユーザー</t>
         </is>
       </c>
       <c r="C145" s="3"/>
@@ -12013,12 +12077,12 @@
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">jboss-cli.sh の接続先 / ログ設定の静的点検と同じく port-offset を考慮 (backend サービスは既定で 19990。--backend-port-offset)。接続できなくても推定で判定する</t>
         </is>
       </c>
       <c r="C146" s="3"/>
@@ -12027,110 +12091,110 @@
     <row r="147" ht="33.0" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">ファイル出力 / 既定で --report-dir 配下の build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md → 一時ディレクトリ (--log-rotation-tz-md で明示、--no-log-rotation-tz-md で抑制。繰り返すと連番)</t>
         </is>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" ht="49.5" customHeight="1">
+    <row r="148" ht="33.0" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
         </is>
       </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" ht="19.5" customHeight="1">
+    <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" ht="49.5" customHeight="1">
+    <row r="150" ht="33.0" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" ht="19.5" customHeight="1">
+    <row r="151" ht="49.5" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" ht="33.0" customHeight="1">
+    <row r="152" ht="19.5" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" ht="33.0" customHeight="1">
+    <row r="153" ht="49.5" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
+          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
+          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
         </is>
       </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" ht="33.0" customHeight="1">
+    <row r="154" ht="19.5" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -12139,40 +12203,40 @@
     <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
         </is>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" ht="19.5" customHeight="1">
+    <row r="156" ht="33.0" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
         </is>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
     </row>
-    <row r="157" ht="33.0" customHeight="1">
+    <row r="157" ht="66.0" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">--report-dir/build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md / --keep-container-mode logs でログローテーションのタイムゾーン点検を実行したとき (既定。--no-log-rotation-tz-md で抑制。--report-dir が無ければ一時ディレクトリ。繰り返すと連番) / 時刻設定の一覧 (区分・項目・値・UTC / JST の判定・集計対象・補足)、判定と集計、指摘と追加情報 (UTC と JST の対応・推奨設定・確認コマンド)、点検の方法、コンテナ内で集めた値 (機微な値は伏せ字)</t>
         </is>
       </c>
       <c r="C157" s="3"/>
@@ -12181,12 +12245,12 @@
     <row r="158" ht="33.0" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C158" s="3"/>
@@ -12195,33 +12259,89 @@
     <row r="159" ht="33.0" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
         </is>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
     </row>
-    <row r="160" ht="33.0" customHeight="1">
+    <row r="160" ht="19.5" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
         </is>
       </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
     </row>
+    <row r="161" ht="33.0" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+    </row>
+    <row r="162" ht="33.0" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+    </row>
+    <row r="163" ht="33.0" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+    </row>
+    <row r="164" ht="33.0" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="59">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -12277,6 +12397,10 @@
     <mergeCell ref="B158:D158"/>
     <mergeCell ref="B159:D159"/>
     <mergeCell ref="B160:D160"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="B162:D162"/>
+    <mergeCell ref="B163:D163"/>
+    <mergeCell ref="B164:D164"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26 19:50:36</t>
+          <t xml:space="preserve">2026-10-10 09:11:20</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" ht="33.0" customHeight="1">
+    <row r="132" ht="66.0" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
+          <t xml:space="preserve">Location ヘッダ確認 / frontend 向け ALB の偽装 (alb-front) のコンテナから、偽装 ALB の HTTPS リスナー経由で frontend の API (対話入力。Enter で既定 /iwinmichl/api/redirect-check/redirect) を呼び、クライアント → ALB が https・ALB → frontend が http で通信していること、ALB が付けた X-Forwarded-Proto: https が JBoss EAP に連携されていること、リダイレクトの Location が https で返ることを区間ごとに判定する。結果をテキストへも出力 / 偽装 ALB (alb-front) 自身を選んだときだけ。偽装 ALB のコンテナ内に python3</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
+          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
         </is>
       </c>
       <c r="C133" s="3"/>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
+          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
         </is>
       </c>
       <c r="C134" s="3"/>
@@ -11928,13 +11928,13 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
+          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
         </is>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" ht="19.5" customHeight="1">
+    <row r="136" ht="33.0" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -11942,21 +11942,21 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
+          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
         </is>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" ht="33.0" customHeight="1">
+    <row r="137" ht="19.5" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
         </is>
       </c>
       <c r="C137" s="3"/>
@@ -11965,26 +11965,26 @@
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" ht="49.5" customHeight="1">
+    <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
+          <t xml:space="preserve">Location ヘッダ確認 (frontend 向け ALB の偽装経由)</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
+          <t xml:space="preserve">入力 / 確認する API のパス。Enter で既定 (偽装 ALB の ALB_FRONT_CHECK_PATH を CLI の default-path で取得。取れなければ /iwinmichl/api/redirect-check/redirect)。/ で始まらない入力・空白を含む入力は聞き直す (3 回まで)</t>
         </is>
       </c>
       <c r="C139" s="3"/>
@@ -11993,26 +11993,26 @@
     <row r="140" ht="33.0" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
+          <t xml:space="preserve">Location ヘッダ確認 (frontend 向け ALB の偽装経由)</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_FRONT_CLI → 既定 /opt/alb-front/alb-front.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" ht="82.5" customHeight="1">
+    <row r="141" ht="33.0" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対象の特定 / 起動中の JVM (argv[0] が java で jboss-modules.jar / -Djboss.home.dir を持つもの) の引数から、ログディレクトリを -Djboss.server.log.dir → -Djboss.server.base.dir 配下の log → -Djboss.home.dir 配下の standalone/log → JBOSS_HOME の候補の順に決める。そこで誰も開いていなければ、実際に server.log* が開かれている場所へ切り替える / JBOSS_HOME は JVM の -Djboss.home.dir → 環境変数 → 既定の候補、設定ファイルは --jboss-config-file → JVM の -c → standalone.xml、デプロイ先は deployment-scanner の path / relative-to</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
         </is>
       </c>
       <c r="C141" s="3"/>
@@ -12021,32 +12021,32 @@
     <row r="142" ht="49.5" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (docker exec -u)。/proc/&lt;pid&gt;/fd は同じユーザーか CAP_SYS_PTRACE でしか読めず、Docker の既定の権限では root でも別ユーザーの FD は見えないため。読めなかったプロセスは [情報] で一覧にする / コンテナの既定ユーザー。権限で読めない cron のディレクトリは [情報] で示す</t>
+          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
         </is>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" ht="99.0" customHeight="1">
+    <row r="143" ht="33.0" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">元のスクリプトからの読み替え / ログディレクトリの自動特定、JVM と同じ uid:gid での実行、収集結果を一時ファイルではなく変数に持つ (読み取り専用のルートでも動く) / WAR / EAR を unzip (Info-ZIP / BusyBox) → python3 → jar → bsdtar → busybox unzip の順で読む (元は unzip だけ)、find が無ければシェルの展開で辿る、use-deployment-logging-config を要素の形 (&lt;… value="false"/&gt;) で判定、起動スクリプトを ENTRYPOINT / CMD から自動で点検 (起動コマンドは標準入力で渡す)、実行時設定を常に取得、jboss-cli.sh の接続先は port-offset を考慮 (backend サービスは既定で 9990 + 10000 = 19990。下記)、jboss.server.log.dir 内の別ファイル (app.log 等) を指すだけなら [情報]</t>
+          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
         </is>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" ht="49.5" customHeight="1">
+    <row r="144" ht="82.5" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
@@ -12054,49 +12054,49 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名に backend を含む (--backend-context と同じ判定) / --backend-port-offset (既定 10000) / --connect --controller=localhost:19990</t>
+          <t xml:space="preserve">対象の特定 / 起動中の JVM (argv[0] が java で jboss-modules.jar / -Djboss.home.dir を持つもの) の引数から、ログディレクトリを -Djboss.server.log.dir → -Djboss.server.base.dir 配下の log → -Djboss.home.dir 配下の standalone/log → JBOSS_HOME の候補の順に決める。そこで誰も開いていなければ、実際に server.log* が開かれている場所へ切り替える / JBOSS_HOME は JVM の -Djboss.home.dir → 環境変数 → 既定の候補、設定ファイルは --jboss-config-file → JVM の -c → standalone.xml、デプロイ先は deployment-scanner の path / relative-to</t>
         </is>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" ht="33.0" customHeight="1">
+    <row r="145" ht="49.5" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (/proc/&lt;pid&gt;/environ を読むため)。検出できなければコンテナの既定ユーザー</t>
+          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (docker exec -u)。/proc/&lt;pid&gt;/fd は同じユーザーか CAP_SYS_PTRACE でしか読めず、Docker の既定の権限では root でも別ユーザーの FD は見えないため。読めなかったプロセスは [情報] で一覧にする / コンテナの既定ユーザー。権限で読めない cron のディレクトリは [情報] で示す</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" ht="33.0" customHeight="1">
+    <row r="146" ht="99.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh の接続先 / ログ設定の静的点検と同じく port-offset を考慮 (backend サービスは既定で 19990。--backend-port-offset)。接続できなくても推定で判定する</t>
+          <t xml:space="preserve">元のスクリプトからの読み替え / ログディレクトリの自動特定、JVM と同じ uid:gid での実行、収集結果を一時ファイルではなく変数に持つ (読み取り専用のルートでも動く) / WAR / EAR を unzip (Info-ZIP / BusyBox) → python3 → jar → bsdtar → busybox unzip の順で読む (元は unzip だけ)、find が無ければシェルの展開で辿る、use-deployment-logging-config を要素の形 (&lt;… value="false"/&gt;) で判定、起動スクリプトを ENTRYPOINT / CMD から自動で点検 (起動コマンドは標準入力で渡す)、実行時設定を常に取得、jboss-cli.sh の接続先は port-offset を考慮 (backend サービスは既定で 9990 + 10000 = 19990。下記)、jboss.server.log.dir 内の別ファイル (app.log 等) を指すだけなら [情報]</t>
         </is>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" ht="33.0" customHeight="1">
+    <row r="147" ht="49.5" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
+          <t xml:space="preserve">server.log の FD 点検 / ログ設定の静的点検 (前日付ファイルへの追記の切り分け)</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル出力 / 既定で --report-dir 配下の build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md → 一時ディレクトリ (--log-rotation-tz-md で明示、--no-log-rotation-tz-md で抑制。繰り返すと連番)</t>
+          <t xml:space="preserve">サービス名に backend を含む (--backend-context と同じ判定) / --backend-port-offset (既定 10000) / --connect --controller=localhost:19990</t>
         </is>
       </c>
       <c r="C147" s="3"/>
@@ -12105,12 +12105,12 @@
     <row r="148" ht="33.0" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
+          <t xml:space="preserve">実行ユーザー / JBoss EAP の JVM と同じ uid:gid (/proc/&lt;pid&gt;/environ を読むため)。検出できなければコンテナの既定ユーザー</t>
         </is>
       </c>
       <c r="C148" s="3"/>
@@ -12119,12 +12119,12 @@
     <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">jboss-cli.sh の接続先 / ログ設定の静的点検と同じく port-offset を考慮 (backend サービスは既定で 19990。--backend-port-offset)。接続できなくても推定で判定する</t>
         </is>
       </c>
       <c r="C149" s="3"/>
@@ -12133,110 +12133,110 @@
     <row r="150" ht="33.0" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (UTC / JST)</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">ファイル出力 / 既定で --report-dir 配下の build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md → 一時ディレクトリ (--log-rotation-tz-md で明示、--no-log-rotation-tz-md で抑制。繰り返すと連番)</t>
         </is>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" ht="49.5" customHeight="1">
+    <row r="151" ht="33.0" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">ディレクトリ構成のツリー (Excel)</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">リンクの先へ降りるか / 降りない (find の既定と同じ)。リンクはツリーの葉として並ぶ</t>
         </is>
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" ht="19.5" customHeight="1">
+    <row r="152" ht="33.0" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" ht="49.5" customHeight="1">
+    <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" ht="19.5" customHeight="1">
+    <row r="154" ht="49.5" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
     </row>
-    <row r="155" ht="33.0" customHeight="1">
+    <row r="155" ht="19.5" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose で何をするのか</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" ht="33.0" customHeight="1">
+    <row r="156" ht="49.5" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
+          <t xml:space="preserve">何が /var/log/messages を増やしているのか</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
+          <t xml:space="preserve">(1) コンテナの標準出力・標準エラー / ログドライバ (docker デーモンの既定、または compose.yml の logging.driver) が journald / syslog の場合、コンテナのログがそのまま /var/log/messages へ流れる / JBoss EAP は起動するだけで数千行。--keep-container-mode で残している間も出続ける</t>
         </is>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
     </row>
-    <row r="157" ht="66.0" customHeight="1">
+    <row r="157" ht="19.5" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir/build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md / --keep-container-mode logs でログローテーションのタイムゾーン点検を実行したとき (既定。--no-log-rotation-tz-md で抑制。--report-dir が無ければ一時ディレクトリ。繰り返すと連番) / 時刻設定の一覧 (区分・項目・値・UTC / JST の判定・集計対象・補足)、判定と集計、指摘と追加情報 (UTC と JST の対応・推奨設定・確認コマンド)、点検の方法、コンテナ内で集めた値 (機微な値は伏せ字)</t>
+          <t xml:space="preserve">停止 / SIGTERM → stopTimeout (既定 30 秒) → SIGKILL / docker stop -t &lt;--ecs-stop-timeout&gt; (同じ手順)</t>
         </is>
       </c>
       <c r="C157" s="3"/>
@@ -12245,12 +12245,12 @@
     <row r="158" ht="33.0" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">compose で何をするのか</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">打ち切り / 失敗タスクが閾値 (必要数の 0.5 倍・最小 3・最大 200) に到達 → ロールバック / --ecs-circuit-breaker-threshold (既定 3) に到達 → 起動確認を失敗として終了</t>
         </is>
       </c>
       <c r="C158" s="3"/>
@@ -12259,26 +12259,26 @@
     <row r="159" ht="33.0" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">判定はいつ出るのか (start_period と起動完了ログの前後関係)</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">起動確認を終えた直後 / 必須コンテナの healthcheck の判定 (healthy / unhealthy) が出るまで待つ。--ecs-essential-service を指定した実行では既定で有効 (--ecs-circuit-breaker-watch / --no-ecs-circuit-breaker-watch で切り替え)</t>
         </is>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
     </row>
-    <row r="160" ht="19.5" customHeight="1">
+    <row r="160" ht="66.0" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">--report-dir/build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md / --keep-container-mode logs でログローテーションのタイムゾーン点検を実行したとき (既定。--no-log-rotation-tz-md で抑制。--report-dir が無ければ一時ディレクトリ。繰り返すと連番) / 時刻設定の一覧 (区分・項目・値・UTC / JST の判定・集計対象・補足)、判定と集計、指摘と追加情報 (UTC と JST の対応・推奨設定・確認コマンド)、点検の方法、コンテナ内で集めた値 (機微な値は伏せ字)</t>
         </is>
       </c>
       <c r="C160" s="3"/>
@@ -12287,12 +12287,12 @@
     <row r="161" ht="33.0" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C161" s="3"/>
@@ -12301,26 +12301,26 @@
     <row r="162" ht="33.0" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
         </is>
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
     </row>
-    <row r="163" ht="33.0" customHeight="1">
+    <row r="163" ht="19.5" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
         </is>
       </c>
       <c r="C163" s="3"/>
@@ -12329,19 +12329,61 @@
     <row r="164" ht="33.0" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
     </row>
+    <row r="165" ht="33.0" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" ht="33.0" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+    </row>
+    <row r="167" ht="33.0" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="62">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -12401,6 +12443,9 @@
     <mergeCell ref="B162:D162"/>
     <mergeCell ref="B163:D163"/>
     <mergeCell ref="B164:D164"/>
+    <mergeCell ref="B165:D165"/>
+    <mergeCell ref="B166:D166"/>
+    <mergeCell ref="B167:D167"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
